--- a/samples/새회사변환예제/01_노바부품_원본원장.xlsx
+++ b/samples/새회사변환예제/01_노바부품_원본원장.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GL_Data" sheetId="1" r:id="R91ef6999e1634262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분개장" sheetId="1" r:id="Re13e1a888f574864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GL_Data" sheetId="2" r:id="R09633c0d78c34f0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +19,7 @@
     <x:numFmt numFmtId="201" formatCode="@"/>
     <x:numFmt numFmtId="202" formatCode="#,##0;(#,##0);0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -30,12 +31,18 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF203B5A"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="맑은 고딕"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -47,10 +54,49 @@
         <x:fgColor rgb="FF203B5A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F5FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F8FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="4">
     <x:border>
       <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
       <x:right/>
       <x:top/>
       <x:bottom/>
@@ -60,29 +106,74 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -286,6 +377,439 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="9" t="str">
+        <x:v>노바부품 분개장</x:v>
+      </x:c>
+      <x:c r="B2" s="10"/>
+      <x:c r="C2" s="10"/>
+      <x:c r="D2" s="10"/>
+      <x:c r="E2" s="10"/>
+      <x:c r="F2" s="10"/>
+      <x:c r="G2" s="10"/>
+      <x:c r="H2" s="10"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="10" t="str">
+        <x:v>2026년 1월 (단위: 원)</x:v>
+      </x:c>
+      <x:c r="B3" s="10"/>
+      <x:c r="C3" s="10"/>
+      <x:c r="D3" s="10"/>
+      <x:c r="E3" s="10"/>
+      <x:c r="F3" s="10"/>
+      <x:c r="G3" s="10"/>
+      <x:c r="H3" s="10"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="11" t="str">
+        <x:v>전기일</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>전표ID</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>차변계정</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>차변코드</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>차변금액</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>대변계정</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>대변코드</x:v>
+      </x:c>
+      <x:c r="H4" s="13" t="str">
+        <x:v>대변금액</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="14" t="d">
+        <x:v>2026-01-02T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>NV26-0001</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="n">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>국내상품매출</x:v>
+      </x:c>
+      <x:c r="G5" s="21" t="str">
+        <x:v>004101</x:v>
+      </x:c>
+      <x:c r="H5" s="22" t="n">
+        <x:v>7000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="14" t="d">
+        <x:v>2026-01-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>NV26-0002</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>신한은행</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>001102</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="n">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G6" s="21" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="H6" s="22" t="n">
+        <x:v>2000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="14" t="d">
+        <x:v>2026-01-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>NV26-0003</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>001301</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="str">
+        <x:v>외상매입대금</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="str">
+        <x:v>002101</x:v>
+      </x:c>
+      <x:c r="H7" s="22" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="14" t="d">
+        <x:v>2026-01-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>NV26-0004</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>매출원가</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>005101</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="str">
+        <x:v>001301</x:v>
+      </x:c>
+      <x:c r="H8" s="22" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="14" t="d">
+        <x:v>2026-01-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>NV26-0005</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>외상매출채권</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>001201</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="n">
+        <x:v>4000000</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="str">
+        <x:v>국내상품매출</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="str">
+        <x:v>004101</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="n">
+        <x:v>4000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="14" t="d">
+        <x:v>2026-01-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>NV26-0006</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="E10" s="19" t="n">
+        <x:v>2500000</x:v>
+      </x:c>
+      <x:c r="F10" s="20" t="str">
+        <x:v>외상매출채권</x:v>
+      </x:c>
+      <x:c r="G10" s="21" t="str">
+        <x:v>001201</x:v>
+      </x:c>
+      <x:c r="H10" s="22" t="n">
+        <x:v>2500000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="14" t="d">
+        <x:v>2026-01-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>NV26-0007</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>외상매입대금</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>002101</x:v>
+      </x:c>
+      <x:c r="E11" s="19" t="n">
+        <x:v>1800000</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="str">
+        <x:v>신한은행</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="str">
+        <x:v>001102</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="n">
+        <x:v>1800000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="14" t="d">
+        <x:v>2026-01-13T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>NV26-0008</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>일반지급수수료</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>005204</x:v>
+      </x:c>
+      <x:c r="E12" s="19" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G12" s="21" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="14" t="d">
+        <x:v>2026-01-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>NV26-0009</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>국내상품매출</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>004101</x:v>
+      </x:c>
+      <x:c r="E13" s="19" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="str">
+        <x:v>외상매출채권</x:v>
+      </x:c>
+      <x:c r="G13" s="21" t="str">
+        <x:v>001201</x:v>
+      </x:c>
+      <x:c r="H13" s="22" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="14" t="d">
+        <x:v>2026-01-16T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>NV26-0010</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>001301</x:v>
+      </x:c>
+      <x:c r="E14" s="19" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="str">
+        <x:v>외상매입대금</x:v>
+      </x:c>
+      <x:c r="G14" s="21" t="str">
+        <x:v>002101</x:v>
+      </x:c>
+      <x:c r="H14" s="22" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="14" t="d">
+        <x:v>2026-01-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>NV26-0011</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>매출원가</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>005101</x:v>
+      </x:c>
+      <x:c r="E15" s="19" t="n">
+        <x:v>700000</x:v>
+      </x:c>
+      <x:c r="F15" s="20" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G15" s="21" t="str">
+        <x:v>001301</x:v>
+      </x:c>
+      <x:c r="H15" s="22" t="n">
+        <x:v>700000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="14" t="d">
+        <x:v>2026-01-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>NV26-0012</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="E16" s="19" t="n">
+        <x:v>2400000</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="str">
+        <x:v>국내상품매출</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="str">
+        <x:v>004101</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="n">
+        <x:v>2400000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="14" t="d">
+        <x:v>2026-01-24T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>NV26-0013</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>일반지급수수료</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="str">
+        <x:v>005204</x:v>
+      </x:c>
+      <x:c r="E17" s="19" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="str">
+        <x:v>001101</x:v>
+      </x:c>
+      <x:c r="H17" s="22" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28" customHeight="1">
+      <x:c r="A18" s="14" t="d">
+        <x:v>2026-01-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>NV26-0014</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>외상매입대금</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>002101</x:v>
+      </x:c>
+      <x:c r="E18" s="19" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G18" s="21" t="str">
+        <x:v>001301</x:v>
+      </x:c>
+      <x:c r="H18" s="22" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
@@ -299,931 +823,931 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="25" t="str">
         <x:v>CorpCode</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="25" t="str">
         <x:v>PostingDate</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="25" t="str">
         <x:v>VoucherNo</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="25" t="str">
         <x:v>LineSeq</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="25" t="str">
         <x:v>GLCode</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="25" t="str">
         <x:v>GLName</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="25" t="str">
         <x:v>Debit_Won</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="25" t="str">
         <x:v>Credit_Won</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="25" t="str">
         <x:v>Memo</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="25" t="str">
         <x:v>EnteredBy</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="d">
+      <x:c r="A2" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="d">
         <x:v>2026-01-02T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>NV26-0001</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
+      <x:c r="D2" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="str">
+      <x:c r="E2" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G2" s="8" t="n">
+      <x:c r="F2" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="n">
         <x:v>7000000</x:v>
       </x:c>
-      <x:c r="H2" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 현금매출</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H2" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="d">
+      <x:c r="A3" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="d">
         <x:v>2026-01-02T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>NV26-0001</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="str">
+      <x:c r="D3" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="str">
+      <x:c r="E3" s="15" t="str">
         <x:v>004101</x:v>
       </x:c>
-      <x:c r="F3" s="2" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>국내상품매출</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="n">
+      <x:c r="G3" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="n">
         <x:v>7000000</x:v>
       </x:c>
-      <x:c r="I3" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 현금매출</x:v>
-      </x:c>
-      <x:c r="J3" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I3" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="d">
+      <x:c r="A4" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="d">
         <x:v>2026-01-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>NV26-0002</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="str">
+      <x:c r="D4" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="str">
+      <x:c r="E4" s="15" t="str">
         <x:v>001102</x:v>
       </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>신한당좌예금</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="n">
+      <x:c r="F4" s="10" t="str">
+        <x:v>신한은행</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" s="2" t="str">
-        <x:v>가상회사 연습 / 은행 계좌 간 이체</x:v>
-      </x:c>
-      <x:c r="J4" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H4" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>차변 신한은행 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="d">
+      <x:c r="A5" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="d">
         <x:v>2026-01-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>NV26-0002</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F5" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="n">
+      <x:c r="F5" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="I5" s="2" t="str">
-        <x:v>가상회사 연습 / 은행 계좌 간 이체</x:v>
-      </x:c>
-      <x:c r="J5" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I5" s="10" t="str">
+        <x:v>차변 신한은행 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="d">
+      <x:c r="A6" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="d">
         <x:v>2026-01-06T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>NV26-0003</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>001301</x:v>
       </x:c>
-      <x:c r="F6" s="2" t="str">
-        <x:v>상품재고</x:v>
-      </x:c>
-      <x:c r="G6" s="8" t="n">
+      <x:c r="F6" s="10" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="n">
         <x:v>3000000</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 외상매입</x:v>
-      </x:c>
-      <x:c r="J6" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H6" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="str">
+        <x:v>차변 재고자산 / 대변 외상매입대금</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="d">
+      <x:c r="A7" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="d">
         <x:v>2026-01-06T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>NV26-0003</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="str">
+      <x:c r="D7" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="str">
+      <x:c r="E7" s="15" t="str">
         <x:v>002101</x:v>
       </x:c>
-      <x:c r="F7" s="2" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>외상매입대금</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="n">
+      <x:c r="G7" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="16" t="n">
         <x:v>3000000</x:v>
       </x:c>
-      <x:c r="I7" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 외상매입</x:v>
-      </x:c>
-      <x:c r="J7" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I7" s="10" t="str">
+        <x:v>차변 재고자산 / 대변 외상매입대금</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="d">
+      <x:c r="A8" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="d">
         <x:v>2026-01-07T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C8" s="2" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>NV26-0004</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="str">
+      <x:c r="D8" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="str">
+      <x:c r="E8" s="15" t="str">
         <x:v>005101</x:v>
       </x:c>
-      <x:c r="F8" s="2" t="str">
-        <x:v>상품매출원가</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="n">
+      <x:c r="F8" s="10" t="str">
+        <x:v>매출원가</x:v>
+      </x:c>
+      <x:c r="G8" s="16" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="2" t="str">
-        <x:v>가상회사 연습 / 판매상품 원가 출고</x:v>
-      </x:c>
-      <x:c r="J8" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H8" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str">
+        <x:v>차변 매출원가 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="d">
+      <x:c r="A9" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="d">
         <x:v>2026-01-07T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C9" s="2" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>NV26-0004</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="str">
+      <x:c r="D9" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="str">
+      <x:c r="E9" s="15" t="str">
         <x:v>001301</x:v>
       </x:c>
-      <x:c r="F9" s="2" t="str">
-        <x:v>상품재고</x:v>
-      </x:c>
-      <x:c r="G9" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="8" t="n">
+      <x:c r="F9" s="10" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="I9" s="2" t="str">
-        <x:v>가상회사 연습 / 판매상품 원가 출고</x:v>
-      </x:c>
-      <x:c r="J9" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I9" s="10" t="str">
+        <x:v>차변 매출원가 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="d">
+      <x:c r="A10" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="d">
         <x:v>2026-01-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>NV26-0005</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="str">
+      <x:c r="D10" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="str">
+      <x:c r="E10" s="15" t="str">
         <x:v>001201</x:v>
       </x:c>
-      <x:c r="F10" s="2" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>외상매출채권</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="n">
+      <x:c r="G10" s="16" t="n">
         <x:v>4000000</x:v>
       </x:c>
-      <x:c r="H10" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 외상매출</x:v>
-      </x:c>
-      <x:c r="J10" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H10" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
+        <x:v>차변 외상매출채권 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="d">
+      <x:c r="A11" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="d">
         <x:v>2026-01-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>NV26-0005</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="str">
+      <x:c r="D11" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="str">
+      <x:c r="E11" s="15" t="str">
         <x:v>004101</x:v>
       </x:c>
-      <x:c r="F11" s="2" t="str">
+      <x:c r="F11" s="10" t="str">
         <x:v>국내상품매출</x:v>
       </x:c>
-      <x:c r="G11" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="8" t="n">
+      <x:c r="G11" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="n">
         <x:v>4000000</x:v>
       </x:c>
-      <x:c r="I11" s="2" t="str">
-        <x:v>가상회사 연습 / 상품 외상매출</x:v>
-      </x:c>
-      <x:c r="J11" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I11" s="10" t="str">
+        <x:v>차변 외상매출채권 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="d">
+      <x:c r="A12" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="d">
         <x:v>2026-01-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>NV26-0006</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="str">
+      <x:c r="D12" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="str">
+      <x:c r="E12" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F12" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G12" s="8" t="n">
+      <x:c r="F12" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="H12" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="2" t="str">
-        <x:v>가상회사 연습 / 매출채권 일부 회수</x:v>
-      </x:c>
-      <x:c r="J12" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H12" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 외상매출채권</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="d">
+      <x:c r="A13" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="d">
         <x:v>2026-01-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="str">
+      <x:c r="C13" s="10" t="str">
         <x:v>NV26-0006</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="str">
+      <x:c r="D13" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="str">
+      <x:c r="E13" s="15" t="str">
         <x:v>001201</x:v>
       </x:c>
-      <x:c r="F13" s="2" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>외상매출채권</x:v>
       </x:c>
-      <x:c r="G13" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="8" t="n">
+      <x:c r="G13" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="I13" s="2" t="str">
-        <x:v>가상회사 연습 / 매출채권 일부 회수</x:v>
-      </x:c>
-      <x:c r="J13" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I13" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 외상매출채권</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="d">
+      <x:c r="A14" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="d">
         <x:v>2026-01-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C14" s="2" t="str">
+      <x:c r="C14" s="10" t="str">
         <x:v>NV26-0007</x:v>
       </x:c>
-      <x:c r="D14" s="7" t="str">
+      <x:c r="D14" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="str">
+      <x:c r="E14" s="15" t="str">
         <x:v>002101</x:v>
       </x:c>
-      <x:c r="F14" s="2" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>외상매입대금</x:v>
       </x:c>
-      <x:c r="G14" s="8" t="n">
+      <x:c r="G14" s="16" t="n">
         <x:v>1800000</x:v>
       </x:c>
-      <x:c r="H14" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="2" t="str">
-        <x:v>가상회사 연습 / 매입대금 지급</x:v>
-      </x:c>
-      <x:c r="J14" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H14" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="str">
+        <x:v>차변 외상매입대금 / 대변 신한은행</x:v>
+      </x:c>
+      <x:c r="J14" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="d">
+      <x:c r="A15" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="d">
         <x:v>2026-01-12T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C15" s="2" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>NV26-0007</x:v>
       </x:c>
-      <x:c r="D15" s="7" t="str">
+      <x:c r="D15" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="str">
+      <x:c r="E15" s="15" t="str">
         <x:v>001102</x:v>
       </x:c>
-      <x:c r="F15" s="2" t="str">
-        <x:v>신한당좌예금</x:v>
-      </x:c>
-      <x:c r="G15" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="8" t="n">
+      <x:c r="F15" s="10" t="str">
+        <x:v>신한은행</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="n">
         <x:v>1800000</x:v>
       </x:c>
-      <x:c r="I15" s="2" t="str">
-        <x:v>가상회사 연습 / 매입대금 지급</x:v>
-      </x:c>
-      <x:c r="J15" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I15" s="10" t="str">
+        <x:v>차변 외상매입대금 / 대변 신한은행</x:v>
+      </x:c>
+      <x:c r="J15" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="d">
+      <x:c r="A16" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="d">
         <x:v>2026-01-13T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C16" s="2" t="str">
+      <x:c r="C16" s="10" t="str">
         <x:v>NV26-0008</x:v>
       </x:c>
-      <x:c r="D16" s="7" t="str">
+      <x:c r="D16" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="str">
+      <x:c r="E16" s="15" t="str">
         <x:v>005204</x:v>
       </x:c>
-      <x:c r="F16" s="2" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>일반지급수수료</x:v>
       </x:c>
-      <x:c r="G16" s="8" t="n">
+      <x:c r="G16" s="16" t="n">
         <x:v>80000</x:v>
       </x:c>
-      <x:c r="H16" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="2" t="str">
-        <x:v>가상회사 연습 / 은행·결제 지급수수료</x:v>
-      </x:c>
-      <x:c r="J16" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="str">
+        <x:v>차변 일반지급수수료 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J16" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="d">
+      <x:c r="A17" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="d">
         <x:v>2026-01-13T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C17" s="2" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>NV26-0008</x:v>
       </x:c>
-      <x:c r="D17" s="7" t="str">
+      <x:c r="D17" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="str">
+      <x:c r="E17" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F17" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G17" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="8" t="n">
+      <x:c r="F17" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="n">
         <x:v>80000</x:v>
       </x:c>
-      <x:c r="I17" s="2" t="str">
-        <x:v>가상회사 연습 / 은행·결제 지급수수료</x:v>
-      </x:c>
-      <x:c r="J17" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I17" s="10" t="str">
+        <x:v>차변 일반지급수수료 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J17" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="d">
+      <x:c r="A18" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="d">
         <x:v>2026-01-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C18" s="2" t="str">
+      <x:c r="C18" s="10" t="str">
         <x:v>NV26-0009</x:v>
       </x:c>
-      <x:c r="D18" s="7" t="str">
+      <x:c r="D18" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="str">
+      <x:c r="E18" s="15" t="str">
         <x:v>004101</x:v>
       </x:c>
-      <x:c r="F18" s="2" t="str">
+      <x:c r="F18" s="10" t="str">
         <x:v>국내상품매출</x:v>
       </x:c>
-      <x:c r="G18" s="8" t="n">
+      <x:c r="G18" s="16" t="n">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="H18" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I18" s="2" t="str">
-        <x:v>가상회사 연습 / 매출 반품 차감</x:v>
-      </x:c>
-      <x:c r="J18" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H18" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="str">
+        <x:v>차변 국내상품매출 / 대변 외상매출채권</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B19" s="6" t="d">
+      <x:c r="A19" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="d">
         <x:v>2026-01-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="str">
+      <x:c r="C19" s="10" t="str">
         <x:v>NV26-0009</x:v>
       </x:c>
-      <x:c r="D19" s="7" t="str">
+      <x:c r="D19" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="str">
+      <x:c r="E19" s="15" t="str">
         <x:v>001201</x:v>
       </x:c>
-      <x:c r="F19" s="2" t="str">
+      <x:c r="F19" s="10" t="str">
         <x:v>외상매출채권</x:v>
       </x:c>
-      <x:c r="G19" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="8" t="n">
+      <x:c r="G19" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="n">
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="I19" s="2" t="str">
-        <x:v>가상회사 연습 / 매출 반품 차감</x:v>
-      </x:c>
-      <x:c r="J19" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I19" s="10" t="str">
+        <x:v>차변 국내상품매출 / 대변 외상매출채권</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="d">
+      <x:c r="A20" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="d">
         <x:v>2026-01-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C20" s="2" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>NV26-0010</x:v>
       </x:c>
-      <x:c r="D20" s="7" t="str">
+      <x:c r="D20" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="str">
+      <x:c r="E20" s="15" t="str">
         <x:v>001301</x:v>
       </x:c>
-      <x:c r="F20" s="2" t="str">
-        <x:v>상품재고</x:v>
-      </x:c>
-      <x:c r="G20" s="8" t="n">
+      <x:c r="F20" s="10" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="H20" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I20" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 상품 외상매입</x:v>
-      </x:c>
-      <x:c r="J20" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H20" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
+        <x:v>차변 재고자산 / 대변 외상매입대금</x:v>
+      </x:c>
+      <x:c r="J20" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B21" s="6" t="d">
+      <x:c r="A21" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="d">
         <x:v>2026-01-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C21" s="2" t="str">
+      <x:c r="C21" s="10" t="str">
         <x:v>NV26-0010</x:v>
       </x:c>
-      <x:c r="D21" s="7" t="str">
+      <x:c r="D21" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="str">
+      <x:c r="E21" s="15" t="str">
         <x:v>002101</x:v>
       </x:c>
-      <x:c r="F21" s="2" t="str">
+      <x:c r="F21" s="10" t="str">
         <x:v>외상매입대금</x:v>
       </x:c>
-      <x:c r="G21" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="8" t="n">
+      <x:c r="G21" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="I21" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 상품 외상매입</x:v>
-      </x:c>
-      <x:c r="J21" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I21" s="10" t="str">
+        <x:v>차변 재고자산 / 대변 외상매입대금</x:v>
+      </x:c>
+      <x:c r="J21" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B22" s="6" t="d">
+      <x:c r="A22" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="d">
         <x:v>2026-01-20T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C22" s="2" t="str">
+      <x:c r="C22" s="10" t="str">
         <x:v>NV26-0011</x:v>
       </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="D22" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E22" s="15" t="str">
         <x:v>005101</x:v>
       </x:c>
-      <x:c r="F22" s="2" t="str">
-        <x:v>상품매출원가</x:v>
-      </x:c>
-      <x:c r="G22" s="8" t="n">
+      <x:c r="F22" s="10" t="str">
+        <x:v>매출원가</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="n">
         <x:v>700000</x:v>
       </x:c>
-      <x:c r="H22" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 판매상품 원가 출고</x:v>
-      </x:c>
-      <x:c r="J22" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H22" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="str">
+        <x:v>차변 매출원가 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J22" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B23" s="6" t="d">
+      <x:c r="A23" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="d">
         <x:v>2026-01-20T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C23" s="2" t="str">
+      <x:c r="C23" s="10" t="str">
         <x:v>NV26-0011</x:v>
       </x:c>
-      <x:c r="D23" s="7" t="str">
+      <x:c r="D23" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="str">
+      <x:c r="E23" s="15" t="str">
         <x:v>001301</x:v>
       </x:c>
-      <x:c r="F23" s="2" t="str">
-        <x:v>상품재고</x:v>
-      </x:c>
-      <x:c r="G23" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="8" t="n">
+      <x:c r="F23" s="10" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="n">
         <x:v>700000</x:v>
       </x:c>
-      <x:c r="I23" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 판매상품 원가 출고</x:v>
-      </x:c>
-      <x:c r="J23" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I23" s="10" t="str">
+        <x:v>차변 매출원가 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J23" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B24" s="6" t="d">
+      <x:c r="A24" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="d">
         <x:v>2026-01-22T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C24" s="2" t="str">
+      <x:c r="C24" s="10" t="str">
         <x:v>NV26-0012</x:v>
       </x:c>
-      <x:c r="D24" s="7" t="str">
+      <x:c r="D24" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="str">
+      <x:c r="E24" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F24" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G24" s="8" t="n">
+      <x:c r="F24" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="n">
         <x:v>2400000</x:v>
       </x:c>
-      <x:c r="H24" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I24" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 상품 현금매출</x:v>
-      </x:c>
-      <x:c r="J24" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H24" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J24" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B25" s="6" t="d">
+      <x:c r="A25" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="d">
         <x:v>2026-01-22T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C25" s="2" t="str">
+      <x:c r="C25" s="10" t="str">
         <x:v>NV26-0012</x:v>
       </x:c>
-      <x:c r="D25" s="7" t="str">
+      <x:c r="D25" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E25" s="7" t="str">
+      <x:c r="E25" s="15" t="str">
         <x:v>004101</x:v>
       </x:c>
-      <x:c r="F25" s="2" t="str">
+      <x:c r="F25" s="10" t="str">
         <x:v>국내상품매출</x:v>
       </x:c>
-      <x:c r="G25" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="8" t="n">
+      <x:c r="G25" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="n">
         <x:v>2400000</x:v>
       </x:c>
-      <x:c r="I25" s="2" t="str">
-        <x:v>가상회사 연습 / 추가 상품 현금매출</x:v>
-      </x:c>
-      <x:c r="J25" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I25" s="10" t="str">
+        <x:v>차변 국민은행 / 대변 국내상품매출</x:v>
+      </x:c>
+      <x:c r="J25" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B26" s="6" t="d">
+      <x:c r="A26" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="d">
         <x:v>2026-01-24T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C26" s="2" t="str">
+      <x:c r="C26" s="10" t="str">
         <x:v>NV26-0013</x:v>
       </x:c>
-      <x:c r="D26" s="7" t="str">
+      <x:c r="D26" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E26" s="7" t="str">
+      <x:c r="E26" s="15" t="str">
         <x:v>005204</x:v>
       </x:c>
-      <x:c r="F26" s="2" t="str">
+      <x:c r="F26" s="10" t="str">
         <x:v>일반지급수수료</x:v>
       </x:c>
-      <x:c r="G26" s="8" t="n">
+      <x:c r="G26" s="16" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="H26" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="2" t="str">
-        <x:v>가상회사 연습 / 주말 수수료 전표 검토 연습</x:v>
-      </x:c>
-      <x:c r="J26" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H26" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="10" t="str">
+        <x:v>차변 일반지급수수료 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J26" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B27" s="6" t="d">
+      <x:c r="A27" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="d">
         <x:v>2026-01-24T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C27" s="2" t="str">
+      <x:c r="C27" s="10" t="str">
         <x:v>NV26-0013</x:v>
       </x:c>
-      <x:c r="D27" s="7" t="str">
+      <x:c r="D27" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="str">
+      <x:c r="E27" s="15" t="str">
         <x:v>001101</x:v>
       </x:c>
-      <x:c r="F27" s="2" t="str">
-        <x:v>국민보통예금</x:v>
-      </x:c>
-      <x:c r="G27" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="8" t="n">
+      <x:c r="F27" s="10" t="str">
+        <x:v>국민은행</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="I27" s="2" t="str">
-        <x:v>가상회사 연습 / 주말 수수료 전표 검토 연습</x:v>
-      </x:c>
-      <x:c r="J27" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I27" s="10" t="str">
+        <x:v>차변 일반지급수수료 / 대변 국민은행</x:v>
+      </x:c>
+      <x:c r="J27" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B28" s="6" t="d">
+      <x:c r="A28" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="d">
         <x:v>2026-01-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C28" s="2" t="str">
+      <x:c r="C28" s="10" t="str">
         <x:v>NV26-0014</x:v>
       </x:c>
-      <x:c r="D28" s="7" t="str">
+      <x:c r="D28" s="15" t="str">
         <x:v>001</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="str">
+      <x:c r="E28" s="15" t="str">
         <x:v>002101</x:v>
       </x:c>
-      <x:c r="F28" s="2" t="str">
+      <x:c r="F28" s="10" t="str">
         <x:v>외상매입대금</x:v>
       </x:c>
-      <x:c r="G28" s="8" t="n">
+      <x:c r="G28" s="16" t="n">
         <x:v>200000</x:v>
       </x:c>
-      <x:c r="H28" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="2" t="str">
-        <x:v>가상회사 연습 / 미판매 상품 매입반품</x:v>
-      </x:c>
-      <x:c r="J28" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="H28" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str">
+        <x:v>차변 외상매입대금 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="2" t="str">
-        <x:v>NOVA_DEMO</x:v>
-      </x:c>
-      <x:c r="B29" s="6" t="d">
+      <x:c r="A29" s="10" t="str">
+        <x:v>NOVA_DEMO</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="d">
         <x:v>2026-01-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C29" s="2" t="str">
+      <x:c r="C29" s="10" t="str">
         <x:v>NV26-0014</x:v>
       </x:c>
-      <x:c r="D29" s="7" t="str">
+      <x:c r="D29" s="15" t="str">
         <x:v>002</x:v>
       </x:c>
-      <x:c r="E29" s="7" t="str">
+      <x:c r="E29" s="15" t="str">
         <x:v>001301</x:v>
       </x:c>
-      <x:c r="F29" s="2" t="str">
-        <x:v>상품재고</x:v>
-      </x:c>
-      <x:c r="G29" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="8" t="n">
+      <x:c r="F29" s="10" t="str">
+        <x:v>재고자산</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="n">
         <x:v>200000</x:v>
       </x:c>
-      <x:c r="I29" s="2" t="str">
-        <x:v>가상회사 연습 / 미판매 상품 매입반품</x:v>
-      </x:c>
-      <x:c r="J29" s="2" t="str">
-        <x:v>더미작성자</x:v>
+      <x:c r="I29" s="10" t="str">
+        <x:v>차변 외상매입대금 / 대변 재고자산</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="str">
+        <x:v>작성자01</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
